--- a/Soluciones_excel.xlsx
+++ b/Soluciones_excel.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c70834368b779c7c/Documentos/CURSOS UNI 26-1/CONTROL ESTADISTICO DEL PROCESO/PC4_Tello_Patrick/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{85108B73-AD35-4A38-B68A-FD787B415C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBEE1B0B-B98B-4085-AE2C-F7426E79F5FD}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{85108B73-AD35-4A38-B68A-FD787B415C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{862F44C0-9807-4D5D-BAB2-6B973881A2F6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{29897C20-D7E8-4588-A092-B9D07C52E4BD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{29897C20-D7E8-4588-A092-B9D07C52E4BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Problema1_XR" sheetId="2" r:id="rId1"/>
     <sheet name="Problema2_u" sheetId="3" r:id="rId2"/>
     <sheet name="Problema3_Capacidad" sheetId="4" r:id="rId3"/>
     <sheet name="Problema4_np" sheetId="5" r:id="rId4"/>
+    <sheet name="Hoja6" sheetId="6" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="155">
   <si>
     <t>Día</t>
   </si>
@@ -504,6 +505,15 @@
   </si>
   <si>
     <t>LCI_np</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Medicion</t>
   </si>
 </sst>
 </file>
@@ -515,7 +525,7 @@
     <numFmt numFmtId="169" formatCode="0.0000"/>
     <numFmt numFmtId="170" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -585,8 +595,26 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF374151"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF030712"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF030712"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -605,8 +633,26 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5E7EB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F4F6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF6FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -629,12 +675,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -708,6 +780,18 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9537,4 +9621,1122 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5C78F88-FC5F-4C9E-88FB-6A6BB2799ACC}">
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="26">
+        <v>1</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="26">
+        <v>2</v>
+      </c>
+      <c r="B3" s="28">
+        <v>1</v>
+      </c>
+      <c r="C3" s="28">
+        <v>-0.29499999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="26">
+        <v>3</v>
+      </c>
+      <c r="B4" s="28">
+        <v>1</v>
+      </c>
+      <c r="C4" s="29">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="26">
+        <v>4</v>
+      </c>
+      <c r="B5" s="28">
+        <v>1</v>
+      </c>
+      <c r="C5" s="28">
+        <v>-0.20499999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="26">
+        <v>5</v>
+      </c>
+      <c r="B6" s="28">
+        <v>1</v>
+      </c>
+      <c r="C6" s="28">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="26">
+        <v>6</v>
+      </c>
+      <c r="B7" s="28">
+        <v>1</v>
+      </c>
+      <c r="C7" s="28">
+        <v>-0.115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="26">
+        <v>7</v>
+      </c>
+      <c r="B8" s="28">
+        <v>2</v>
+      </c>
+      <c r="C8" s="28">
+        <v>-0.2762</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="26">
+        <v>8</v>
+      </c>
+      <c r="B9" s="28">
+        <v>2</v>
+      </c>
+      <c r="C9" s="28">
+        <v>-0.23130000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="26">
+        <v>9</v>
+      </c>
+      <c r="B10" s="28">
+        <v>2</v>
+      </c>
+      <c r="C10" s="28">
+        <v>-0.18629999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26">
+        <v>10</v>
+      </c>
+      <c r="B11" s="28">
+        <v>2</v>
+      </c>
+      <c r="C11" s="28">
+        <v>-0.14130000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26">
+        <v>11</v>
+      </c>
+      <c r="B12" s="28">
+        <v>2</v>
+      </c>
+      <c r="C12" s="28">
+        <v>-9.6299999999999997E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26">
+        <v>12</v>
+      </c>
+      <c r="B13" s="28">
+        <v>3</v>
+      </c>
+      <c r="C13" s="28">
+        <v>-0.25750000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="26">
+        <v>13</v>
+      </c>
+      <c r="B14" s="28">
+        <v>3</v>
+      </c>
+      <c r="C14" s="28">
+        <v>-0.21249999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="26">
+        <v>14</v>
+      </c>
+      <c r="B15" s="28">
+        <v>3</v>
+      </c>
+      <c r="C15" s="28">
+        <v>-0.16750000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26">
+        <v>15</v>
+      </c>
+      <c r="B16" s="28">
+        <v>3</v>
+      </c>
+      <c r="C16" s="28">
+        <v>-0.1225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="26">
+        <v>16</v>
+      </c>
+      <c r="B17" s="28">
+        <v>3</v>
+      </c>
+      <c r="C17" s="28">
+        <v>-7.7499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="26">
+        <v>17</v>
+      </c>
+      <c r="B18" s="28">
+        <v>4</v>
+      </c>
+      <c r="C18" s="28">
+        <v>-0.23880000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="26">
+        <v>18</v>
+      </c>
+      <c r="B19" s="28">
+        <v>4</v>
+      </c>
+      <c r="C19" s="28">
+        <v>-0.1938</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26">
+        <v>19</v>
+      </c>
+      <c r="B20" s="28">
+        <v>4</v>
+      </c>
+      <c r="C20" s="28">
+        <v>-0.14879999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26">
+        <v>20</v>
+      </c>
+      <c r="B21" s="28">
+        <v>4</v>
+      </c>
+      <c r="C21" s="28">
+        <v>-0.1038</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="26">
+        <v>21</v>
+      </c>
+      <c r="B22" s="28">
+        <v>4</v>
+      </c>
+      <c r="C22" s="28">
+        <v>-5.8799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="26">
+        <v>22</v>
+      </c>
+      <c r="B23" s="28">
+        <v>5</v>
+      </c>
+      <c r="C23" s="28">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="26">
+        <v>23</v>
+      </c>
+      <c r="B24" s="28">
+        <v>5</v>
+      </c>
+      <c r="C24" s="28">
+        <v>-0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="26">
+        <v>24</v>
+      </c>
+      <c r="B25" s="28">
+        <v>5</v>
+      </c>
+      <c r="C25" s="28">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="28">
+        <v>5</v>
+      </c>
+      <c r="C26" s="28">
+        <v>-8.5000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="26">
+        <v>26</v>
+      </c>
+      <c r="B27" s="28">
+        <v>5</v>
+      </c>
+      <c r="C27" s="28">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="26">
+        <v>27</v>
+      </c>
+      <c r="B28" s="28">
+        <v>6</v>
+      </c>
+      <c r="C28" s="28">
+        <v>-0.20119999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="26">
+        <v>28</v>
+      </c>
+      <c r="B29" s="28">
+        <v>6</v>
+      </c>
+      <c r="C29" s="28">
+        <v>-0.15620000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="26">
+        <v>29</v>
+      </c>
+      <c r="B30" s="28">
+        <v>6</v>
+      </c>
+      <c r="C30" s="28">
+        <v>-0.1113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="26">
+        <v>30</v>
+      </c>
+      <c r="B31" s="28">
+        <v>6</v>
+      </c>
+      <c r="C31" s="28">
+        <v>-6.6299999999999998E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="26">
+        <v>31</v>
+      </c>
+      <c r="B32" s="28">
+        <v>6</v>
+      </c>
+      <c r="C32" s="28">
+        <v>-2.1299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="26">
+        <v>32</v>
+      </c>
+      <c r="B33" s="28">
+        <v>7</v>
+      </c>
+      <c r="C33" s="28">
+        <v>-0.1825</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="26">
+        <v>33</v>
+      </c>
+      <c r="B34" s="28">
+        <v>7</v>
+      </c>
+      <c r="C34" s="28">
+        <v>-0.13750000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="26">
+        <v>34</v>
+      </c>
+      <c r="B35" s="28">
+        <v>7</v>
+      </c>
+      <c r="C35" s="28">
+        <v>-9.2499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="26">
+        <v>35</v>
+      </c>
+      <c r="B36" s="28">
+        <v>7</v>
+      </c>
+      <c r="C36" s="28">
+        <v>-4.7500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="26">
+        <v>36</v>
+      </c>
+      <c r="B37" s="28">
+        <v>7</v>
+      </c>
+      <c r="C37" s="28">
+        <v>-2.5000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="26">
+        <v>37</v>
+      </c>
+      <c r="B38" s="28">
+        <v>8</v>
+      </c>
+      <c r="C38" s="28">
+        <v>-0.1638</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="26">
+        <v>38</v>
+      </c>
+      <c r="B39" s="28">
+        <v>8</v>
+      </c>
+      <c r="C39" s="28">
+        <v>-0.1187</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="26">
+        <v>39</v>
+      </c>
+      <c r="B40" s="28">
+        <v>8</v>
+      </c>
+      <c r="C40" s="28">
+        <v>-7.3700000000000002E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="26">
+        <v>40</v>
+      </c>
+      <c r="B41" s="28">
+        <v>8</v>
+      </c>
+      <c r="C41" s="28">
+        <v>-2.87E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="26">
+        <v>41</v>
+      </c>
+      <c r="B42" s="28">
+        <v>8</v>
+      </c>
+      <c r="C42" s="28">
+        <v>1.6299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="26">
+        <v>42</v>
+      </c>
+      <c r="B43" s="28">
+        <v>9</v>
+      </c>
+      <c r="C43" s="28">
+        <v>-0.14499999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="26">
+        <v>43</v>
+      </c>
+      <c r="B44" s="28">
+        <v>9</v>
+      </c>
+      <c r="C44" s="28">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="26">
+        <v>44</v>
+      </c>
+      <c r="B45" s="28">
+        <v>9</v>
+      </c>
+      <c r="C45" s="28">
+        <v>-5.5E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="26">
+        <v>45</v>
+      </c>
+      <c r="B46" s="28">
+        <v>9</v>
+      </c>
+      <c r="C46" s="28">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="26">
+        <v>46</v>
+      </c>
+      <c r="B47" s="28">
+        <v>9</v>
+      </c>
+      <c r="C47" s="28">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="26">
+        <v>47</v>
+      </c>
+      <c r="B48" s="28">
+        <v>10</v>
+      </c>
+      <c r="C48" s="28">
+        <v>-0.1263</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="26">
+        <v>48</v>
+      </c>
+      <c r="B49" s="28">
+        <v>10</v>
+      </c>
+      <c r="C49" s="28">
+        <v>-8.1299999999999997E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="26">
+        <v>49</v>
+      </c>
+      <c r="B50" s="28">
+        <v>10</v>
+      </c>
+      <c r="C50" s="28">
+        <v>-3.6299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="26">
+        <v>50</v>
+      </c>
+      <c r="B51" s="28">
+        <v>10</v>
+      </c>
+      <c r="C51" s="28">
+        <v>8.6999999999999994E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="26">
+        <v>51</v>
+      </c>
+      <c r="B52" s="28">
+        <v>10</v>
+      </c>
+      <c r="C52" s="28">
+        <v>5.3699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="26">
+        <v>52</v>
+      </c>
+      <c r="B53" s="28">
+        <v>11</v>
+      </c>
+      <c r="C53" s="28">
+        <v>-0.1075</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="26">
+        <v>53</v>
+      </c>
+      <c r="B54" s="28">
+        <v>11</v>
+      </c>
+      <c r="C54" s="28">
+        <v>-6.25E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="26">
+        <v>54</v>
+      </c>
+      <c r="B55" s="28">
+        <v>11</v>
+      </c>
+      <c r="C55" s="28">
+        <v>-1.7500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="26">
+        <v>55</v>
+      </c>
+      <c r="B56" s="28">
+        <v>11</v>
+      </c>
+      <c r="C56" s="28">
+        <v>2.75E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="26">
+        <v>56</v>
+      </c>
+      <c r="B57" s="28">
+        <v>11</v>
+      </c>
+      <c r="C57" s="28">
+        <v>7.2499999999999995E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="26">
+        <v>57</v>
+      </c>
+      <c r="B58" s="28">
+        <v>12</v>
+      </c>
+      <c r="C58" s="28">
+        <v>-8.8800000000000004E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="26">
+        <v>58</v>
+      </c>
+      <c r="B59" s="28">
+        <v>12</v>
+      </c>
+      <c r="C59" s="28">
+        <v>-4.3799999999999999E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="26">
+        <v>59</v>
+      </c>
+      <c r="B60" s="28">
+        <v>12</v>
+      </c>
+      <c r="C60" s="28">
+        <v>1.1999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="26">
+        <v>60</v>
+      </c>
+      <c r="B61" s="28">
+        <v>12</v>
+      </c>
+      <c r="C61" s="28">
+        <v>4.6199999999999998E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="26">
+        <v>61</v>
+      </c>
+      <c r="B62" s="28">
+        <v>12</v>
+      </c>
+      <c r="C62" s="28">
+        <v>9.1200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="26">
+        <v>62</v>
+      </c>
+      <c r="B63" s="28">
+        <v>13</v>
+      </c>
+      <c r="C63" s="28">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="26">
+        <v>63</v>
+      </c>
+      <c r="B64" s="28">
+        <v>13</v>
+      </c>
+      <c r="C64" s="28">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="26">
+        <v>64</v>
+      </c>
+      <c r="B65" s="28">
+        <v>13</v>
+      </c>
+      <c r="C65" s="28">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="26">
+        <v>65</v>
+      </c>
+      <c r="B66" s="28">
+        <v>13</v>
+      </c>
+      <c r="C66" s="28">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="26">
+        <v>66</v>
+      </c>
+      <c r="B67" s="28">
+        <v>13</v>
+      </c>
+      <c r="C67" s="28">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="26">
+        <v>67</v>
+      </c>
+      <c r="B68" s="28">
+        <v>14</v>
+      </c>
+      <c r="C68" s="28">
+        <v>-5.1299999999999998E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="26">
+        <v>68</v>
+      </c>
+      <c r="B69" s="28">
+        <v>14</v>
+      </c>
+      <c r="C69" s="28">
+        <v>-6.3E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="26">
+        <v>69</v>
+      </c>
+      <c r="B70" s="28">
+        <v>14</v>
+      </c>
+      <c r="C70" s="28">
+        <v>3.8699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="26">
+        <v>70</v>
+      </c>
+      <c r="B71" s="28">
+        <v>14</v>
+      </c>
+      <c r="C71" s="28">
+        <v>8.3699999999999997E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="26">
+        <v>71</v>
+      </c>
+      <c r="B72" s="28">
+        <v>14</v>
+      </c>
+      <c r="C72" s="28">
+        <v>0.12870000000000001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="26">
+        <v>72</v>
+      </c>
+      <c r="B73" s="28">
+        <v>15</v>
+      </c>
+      <c r="C73" s="28">
+        <v>-3.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="26">
+        <v>73</v>
+      </c>
+      <c r="B74" s="28">
+        <v>15</v>
+      </c>
+      <c r="C74" s="28">
+        <v>1.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="26">
+        <v>74</v>
+      </c>
+      <c r="B75" s="28">
+        <v>15</v>
+      </c>
+      <c r="C75" s="28">
+        <v>5.7500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="26">
+        <v>75</v>
+      </c>
+      <c r="B76" s="28">
+        <v>15</v>
+      </c>
+      <c r="C76" s="28">
+        <v>0.10249999999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="26">
+        <v>76</v>
+      </c>
+      <c r="B77" s="28">
+        <v>15</v>
+      </c>
+      <c r="C77" s="28">
+        <v>0.14749999999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="26">
+        <v>77</v>
+      </c>
+      <c r="B78" s="28">
+        <v>16</v>
+      </c>
+      <c r="C78" s="28">
+        <v>-1.37E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="26">
+        <v>78</v>
+      </c>
+      <c r="B79" s="28">
+        <v>16</v>
+      </c>
+      <c r="C79" s="28">
+        <v>3.1199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="26">
+        <v>79</v>
+      </c>
+      <c r="B80" s="28">
+        <v>16</v>
+      </c>
+      <c r="C80" s="28">
+        <v>7.6200000000000004E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="26">
+        <v>80</v>
+      </c>
+      <c r="B81" s="28">
+        <v>16</v>
+      </c>
+      <c r="C81" s="28">
+        <v>0.1212</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="26">
+        <v>81</v>
+      </c>
+      <c r="B82" s="28">
+        <v>16</v>
+      </c>
+      <c r="C82" s="28">
+        <v>0.1663</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="26">
+        <v>82</v>
+      </c>
+      <c r="B83" s="28">
+        <v>17</v>
+      </c>
+      <c r="C83" s="28">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="26">
+        <v>83</v>
+      </c>
+      <c r="B84" s="28">
+        <v>17</v>
+      </c>
+      <c r="C84" s="28">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="26">
+        <v>84</v>
+      </c>
+      <c r="B85" s="28">
+        <v>17</v>
+      </c>
+      <c r="C85" s="28">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="26">
+        <v>85</v>
+      </c>
+      <c r="B86" s="28">
+        <v>17</v>
+      </c>
+      <c r="C86" s="28">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="26">
+        <v>86</v>
+      </c>
+      <c r="B87" s="28">
+        <v>17</v>
+      </c>
+      <c r="C87" s="28">
+        <v>0.185</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="26">
+        <v>87</v>
+      </c>
+      <c r="B88" s="28">
+        <v>18</v>
+      </c>
+      <c r="C88" s="28">
+        <v>2.3699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="26">
+        <v>88</v>
+      </c>
+      <c r="B89" s="28">
+        <v>18</v>
+      </c>
+      <c r="C89" s="28">
+        <v>6.8699999999999997E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="26">
+        <v>89</v>
+      </c>
+      <c r="B90" s="28">
+        <v>18</v>
+      </c>
+      <c r="C90" s="28">
+        <v>0.1137</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="26">
+        <v>90</v>
+      </c>
+      <c r="B91" s="28">
+        <v>18</v>
+      </c>
+      <c r="C91" s="28">
+        <v>0.15870000000000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="26">
+        <v>91</v>
+      </c>
+      <c r="B92" s="28">
+        <v>18</v>
+      </c>
+      <c r="C92" s="28">
+        <v>0.20369999999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A93" s="26">
+        <v>92</v>
+      </c>
+      <c r="B93" s="28">
+        <v>19</v>
+      </c>
+      <c r="C93" s="28">
+        <v>4.2500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="26">
+        <v>93</v>
+      </c>
+      <c r="B94" s="28">
+        <v>19</v>
+      </c>
+      <c r="C94" s="28">
+        <v>8.7499999999999994E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A95" s="26">
+        <v>94</v>
+      </c>
+      <c r="B95" s="28">
+        <v>19</v>
+      </c>
+      <c r="C95" s="28">
+        <v>0.13250000000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="26">
+        <v>95</v>
+      </c>
+      <c r="B96" s="28">
+        <v>19</v>
+      </c>
+      <c r="C96" s="28">
+        <v>0.17749999999999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A97" s="26">
+        <v>96</v>
+      </c>
+      <c r="B97" s="28">
+        <v>19</v>
+      </c>
+      <c r="C97" s="28">
+        <v>0.2225</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="26">
+        <v>97</v>
+      </c>
+      <c r="B98" s="28">
+        <v>20</v>
+      </c>
+      <c r="C98" s="28">
+        <v>6.1199999999999997E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="26">
+        <v>98</v>
+      </c>
+      <c r="B99" s="28">
+        <v>20</v>
+      </c>
+      <c r="C99" s="28">
+        <v>0.1062</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="26">
+        <v>99</v>
+      </c>
+      <c r="B100" s="28">
+        <v>20</v>
+      </c>
+      <c r="C100" s="28">
+        <v>0.1512</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A101" s="26">
+        <v>100</v>
+      </c>
+      <c r="B101" s="28">
+        <v>20</v>
+      </c>
+      <c r="C101" s="28">
+        <v>0.19620000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>